--- a/codespace/results/ch4_fw2_stress_profile.xlsx
+++ b/codespace/results/ch4_fw2_stress_profile.xlsx
@@ -470,16 +470,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2886570017076439</v>
+        <v>0.3004113533694679</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2886570017076439</v>
+        <v>0.3004113533694679</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2886575346007401</v>
+        <v>0.3004115676505014</v>
       </c>
       <c r="F2" t="n">
-        <v>2.163812853839264e-05</v>
+        <v>3.255684586922492e-07</v>
       </c>
     </row>
     <row r="3">
@@ -492,16 +492,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>0.153283714107101</v>
+        <v>0.1548197441492005</v>
       </c>
       <c r="D3" t="n">
-        <v>0.153283714107101</v>
+        <v>0.1548197441492005</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1532866743209017</v>
+        <v>0.1548235368123086</v>
       </c>
       <c r="F3" t="n">
-        <v>5.478970364403146e-06</v>
+        <v>0.00144153748577372</v>
       </c>
     </row>
     <row r="4">
@@ -514,16 +514,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>0.08964361381031144</v>
+        <v>0.09006605609571285</v>
       </c>
       <c r="D4" t="n">
-        <v>0.08964361381031144</v>
+        <v>0.09006605609571285</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0896912700046341</v>
+        <v>0.0900749962166819</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001125685297567874</v>
+        <v>2.648242968908421e-05</v>
       </c>
     </row>
     <row r="5">
@@ -536,16 +536,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>0.06616395651331113</v>
+        <v>0.06637801459301726</v>
       </c>
       <c r="D5" t="n">
-        <v>0.06616395651331113</v>
+        <v>0.06637801459301726</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06619999636045455</v>
+        <v>0.06637889885830604</v>
       </c>
       <c r="F5" t="n">
-        <v>6.680238363432345e-05</v>
+        <v>1.168329363830656e-05</v>
       </c>
     </row>
     <row r="6">
@@ -558,16 +558,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>0.05196618042564231</v>
+        <v>0.05230353570640549</v>
       </c>
       <c r="D6" t="n">
-        <v>0.05196618042564231</v>
+        <v>0.05230353570640549</v>
       </c>
       <c r="E6" t="n">
-        <v>0.05197290582332248</v>
+        <v>0.05231125225317703</v>
       </c>
       <c r="F6" t="n">
-        <v>1.156551237561226e-05</v>
+        <v>2.102950551108318e-05</v>
       </c>
     </row>
     <row r="7">
@@ -580,16 +580,16 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2890412792040734</v>
+        <v>0.2899609234096011</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2890412792040734</v>
+        <v>0.2899609234096011</v>
       </c>
       <c r="E7" t="n">
-        <v>0.289041347751855</v>
+        <v>0.2899609493286637</v>
       </c>
       <c r="F7" t="n">
-        <v>2.673321731760936e-07</v>
+        <v>2.949741118030147e-08</v>
       </c>
     </row>
     <row r="8">
@@ -602,16 +602,16 @@
         <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1285211907445795</v>
+        <v>0.1281787496296083</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1285211907445795</v>
+        <v>0.1281787496296083</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1285387190128746</v>
+        <v>0.1281791804236158</v>
       </c>
       <c r="F8" t="n">
-        <v>4.186290921032176e-05</v>
+        <v>6.939011481799096e-07</v>
       </c>
     </row>
     <row r="9">
@@ -624,16 +624,16 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>0.07794935556102532</v>
+        <v>0.07527216848308728</v>
       </c>
       <c r="D9" t="n">
-        <v>0.07794935556102532</v>
+        <v>0.07527216848308728</v>
       </c>
       <c r="E9" t="n">
-        <v>0.07795812398499741</v>
+        <v>0.07527354472621203</v>
       </c>
       <c r="F9" t="n">
-        <v>9.305966443703961e-06</v>
+        <v>1.573497649329236e-06</v>
       </c>
     </row>
     <row r="10">
@@ -646,16 +646,16 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>0.05608610663898055</v>
+        <v>0.05291500574094519</v>
       </c>
       <c r="D10" t="n">
-        <v>0.05608610663898055</v>
+        <v>0.05291500574094519</v>
       </c>
       <c r="E10" t="n">
-        <v>0.05609246377050462</v>
+        <v>0.05292164595154888</v>
       </c>
       <c r="F10" t="n">
-        <v>1.533949284724528e-05</v>
+        <v>1.395244059648054e-05</v>
       </c>
     </row>
     <row r="11">
@@ -668,16 +668,16 @@
         <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>0.04556717560093095</v>
+        <v>0.04389802713875149</v>
       </c>
       <c r="D11" t="n">
-        <v>0.04556717560093095</v>
+        <v>0.04389802713875149</v>
       </c>
       <c r="E11" t="n">
-        <v>0.04557133998278538</v>
+        <v>0.04391723995539944</v>
       </c>
       <c r="F11" t="n">
-        <v>6.902870426622743e-06</v>
+        <v>9.049429798333591e-05</v>
       </c>
     </row>
   </sheetData>
